--- a/cliente_banco_tabajara.xlsx
+++ b/cliente_banco_tabajara.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,11 +451,13 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>well</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>12356</v>
+          <t>wejjsk</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -469,32 +471,6 @@
         <v>400</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>raumdo</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>4567798</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>salario</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>401</v>
-      </c>
-      <c r="F3" t="n">
         <v>0</v>
       </c>
     </row>
